--- a/backend/data/ST2137_Questions.xlsx
+++ b/backend/data/ST2137_Questions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhixin/Documents/y4s1/dsa3101/extracted_questions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhixin/Documents/y4s1/dsa3101/dsa3101-2510-quiz-02/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E93F648-9C76-E04F-971E-CC3052C7DA04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9ACECD-6866-264B-B7A1-4FCAAC58AF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="16660" activeTab="1" xr2:uid="{CA20E2D9-AC26-2B4B-A400-E03C0BFEE2BC}"/>
   </bookViews>
@@ -39,9 +39,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="93">
   <si>
-    <t>Context ID</t>
-  </si>
-  <si>
     <t>Context Text</t>
   </si>
   <si>
@@ -91,9 +88,6 @@
   </si>
   <si>
     <t>Code</t>
-  </si>
-  <si>
-    <t>Hard</t>
   </si>
   <si>
     <t>This question is to be answered using Python.
@@ -402,15 +396,28 @@
   <si>
     <t>Basic Concepts in Statistics, Data Manipulation</t>
   </si>
+  <si>
+    <t>Context ID</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -436,11 +443,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -779,14 +787,14 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -809,52 +817,52 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" t="s">
-        <v>12</v>
-      </c>
       <c r="P1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="404" x14ac:dyDescent="0.2">
@@ -862,19 +870,19 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M2">
         <v>8</v>
       </c>
       <c r="N2" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="O2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="170" x14ac:dyDescent="0.2">
@@ -882,10 +890,10 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>0.5</v>
@@ -900,16 +908,16 @@
         <v>0.22800000000000001</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M3">
         <v>1</v>
       </c>
       <c r="N3" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="O3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="85" x14ac:dyDescent="0.2">
@@ -917,37 +925,37 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
         <v>23</v>
       </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
         <v>25</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>26</v>
       </c>
-      <c r="H4" t="s">
+      <c r="K4" t="s">
         <v>27</v>
       </c>
-      <c r="I4" t="s">
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4" t="s">
         <v>28</v>
       </c>
-      <c r="K4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-      <c r="N4" t="s">
-        <v>30</v>
-      </c>
       <c r="O4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="221" x14ac:dyDescent="0.2">
@@ -955,19 +963,19 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M5">
         <v>8</v>
       </c>
       <c r="N5" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="O5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="136" x14ac:dyDescent="0.2">
@@ -975,19 +983,19 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M6">
         <v>4</v>
       </c>
       <c r="N6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" t="s">
+        <v>73</v>
+      </c>
+      <c r="P6" t="s">
         <v>32</v>
-      </c>
-      <c r="O6" t="s">
-        <v>75</v>
-      </c>
-      <c r="P6" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -995,37 +1003,37 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" t="s">
         <v>35</v>
       </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>36</v>
       </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
         <v>37</v>
       </c>
-      <c r="H7" t="s">
+      <c r="K7" t="s">
         <v>38</v>
       </c>
-      <c r="I7" t="s">
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7" t="s">
+        <v>28</v>
+      </c>
+      <c r="O7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P7" t="s">
         <v>39</v>
-      </c>
-      <c r="K7" t="s">
-        <v>40</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O7" t="s">
-        <v>78</v>
-      </c>
-      <c r="P7" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="289" x14ac:dyDescent="0.2">
@@ -1033,22 +1041,22 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="O8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="P8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -1056,10 +1064,10 @@
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F9">
         <v>6</v>
@@ -1074,16 +1082,16 @@
         <v>2</v>
       </c>
       <c r="K9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M9">
         <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -1091,34 +1099,34 @@
         <v>11</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" t="s">
         <v>46</v>
       </c>
-      <c r="E10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>47</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>48</v>
       </c>
-      <c r="H10" t="s">
-        <v>49</v>
-      </c>
-      <c r="I10" t="s">
-        <v>50</v>
-      </c>
       <c r="K10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M10">
         <v>1</v>
       </c>
       <c r="N10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="255" x14ac:dyDescent="0.2">
@@ -1126,19 +1134,19 @@
         <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M11">
         <v>4</v>
       </c>
       <c r="N11" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="O11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="102" x14ac:dyDescent="0.2">
@@ -1146,19 +1154,19 @@
         <v>14</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M12">
         <v>4</v>
       </c>
       <c r="N12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -1166,10 +1174,10 @@
         <v>15</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F13">
         <v>3</v>
@@ -1184,16 +1192,16 @@
         <v>6</v>
       </c>
       <c r="K13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M13">
         <v>1</v>
       </c>
       <c r="N13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="255" x14ac:dyDescent="0.2">
@@ -1201,19 +1209,19 @@
         <v>16</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M14">
         <v>6</v>
       </c>
       <c r="N14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -1221,19 +1229,19 @@
         <v>18</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M15">
         <v>3</v>
       </c>
       <c r="N15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="85" x14ac:dyDescent="0.2">
@@ -1241,19 +1249,19 @@
         <v>20</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M16">
         <v>3</v>
       </c>
       <c r="N16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="2:15" ht="85" x14ac:dyDescent="0.2">
@@ -1261,10 +1269,10 @@
         <v>22</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -1273,16 +1281,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M17">
         <v>1</v>
       </c>
       <c r="N17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="2:15" ht="17" x14ac:dyDescent="0.2">
@@ -1290,34 +1298,34 @@
         <v>23</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" t="s">
         <v>59</v>
       </c>
-      <c r="E18" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="H18" t="s">
         <v>60</v>
       </c>
-      <c r="G18" t="s">
+      <c r="I18" t="s">
         <v>61</v>
       </c>
-      <c r="H18" t="s">
-        <v>62</v>
-      </c>
-      <c r="I18" t="s">
-        <v>63</v>
-      </c>
       <c r="K18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M18">
         <v>1</v>
       </c>
       <c r="N18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O18" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="2:15" ht="68" x14ac:dyDescent="0.2">
@@ -1325,10 +1333,10 @@
         <v>24</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -1337,16 +1345,16 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M19">
         <v>1</v>
       </c>
       <c r="N19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O19" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="2:15" ht="51" x14ac:dyDescent="0.2">
@@ -1354,10 +1362,10 @@
         <v>27</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -1366,16 +1374,16 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M20">
         <v>1</v>
       </c>
       <c r="N20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="2:15" ht="136" x14ac:dyDescent="0.2">
@@ -1383,28 +1391,28 @@
         <v>28</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21" t="s">
         <v>66</v>
       </c>
-      <c r="E21" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21" t="s">
-        <v>68</v>
-      </c>
       <c r="K21" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M21">
         <v>1</v>
       </c>
       <c r="N21" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="2:15" ht="51" x14ac:dyDescent="0.2">
@@ -1412,10 +1420,10 @@
         <v>29</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1424,16 +1432,16 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M22">
         <v>1</v>
       </c>
       <c r="N22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O22" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="2:15" ht="17" x14ac:dyDescent="0.2">
@@ -1441,34 +1449,34 @@
         <v>30</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" t="s">
         <v>70</v>
       </c>
-      <c r="E23" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="H23" t="s">
         <v>71</v>
       </c>
-      <c r="G23" t="s">
+      <c r="I23" t="s">
         <v>72</v>
       </c>
-      <c r="H23" t="s">
-        <v>73</v>
-      </c>
-      <c r="I23" t="s">
-        <v>74</v>
-      </c>
       <c r="K23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M23">
         <v>1</v>
       </c>
       <c r="N23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O23" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
